--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N69_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N69_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.55159680411244</v>
+        <v>2.202134480668271</v>
       </c>
       <c r="D2" t="n">
-        <v>5.315072906367325</v>
+        <v>0.8636993472846903</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
